--- a/data/cox_xlsx/BETCO.CO.xlsx
+++ b/data/cox_xlsx/BETCO.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="335">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -673,6 +673,12 @@
   </si>
   <si>
     <t>Capitalized Leases</t>
+  </si>
+  <si>
+    <t>Debt to Mortgage Credit Institutions LT</t>
+  </si>
+  <si>
+    <t>Debt to Credit Institutions LT</t>
   </si>
   <si>
     <t>Balancing Item - Current Liabilities</t>
@@ -1143,7 +1149,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1221,6 +1227,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -8616,8 +8625,8 @@
       <c r="L92" s="19"/>
     </row>
     <row r="93" ht="15.0" customHeight="1">
-      <c r="A93" s="14" t="s">
-        <v>202</v>
+      <c r="A93" s="26" t="s">
+        <v>218</v>
       </c>
       <c r="B93" s="19"/>
       <c r="C93" s="19"/>
@@ -8640,8 +8649,8 @@
       <c r="L93" s="19"/>
     </row>
     <row r="94" ht="15.0" customHeight="1">
-      <c r="A94" s="14" t="s">
-        <v>203</v>
+      <c r="A94" s="26" t="s">
+        <v>219</v>
       </c>
       <c r="B94" s="19"/>
       <c r="C94" s="19">
@@ -8671,7 +8680,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B95" s="19"/>
       <c r="C95" s="19"/>
@@ -8697,7 +8706,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="16" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B96" s="17">
         <v>740.4</v>
@@ -8735,7 +8744,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
@@ -8755,7 +8764,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="16" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B98" s="17">
         <v>5234.99</v>
@@ -8793,7 +8802,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="16" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B99" s="25">
         <v>12689.67</v>
@@ -8831,7 +8840,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B100" s="18">
         <v>3.28</v>
@@ -8869,7 +8878,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B101" s="18">
         <v>58.68</v>
@@ -8907,7 +8916,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B102" s="18">
         <v>61.96</v>
@@ -8945,7 +8954,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B103" s="19"/>
       <c r="C103" s="15">
@@ -8971,7 +8980,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B104" s="15">
         <v>3071.0</v>
@@ -8999,7 +9008,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B105" s="19">
         <v>0.0</v>
@@ -9027,7 +9036,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B106" s="15">
         <v>3071.0</v>
@@ -9053,7 +9062,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B107" s="15">
         <v>3068.1</v>
@@ -9081,7 +9090,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B108" s="15">
         <v>700.57</v>
@@ -9105,7 +9114,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B109" s="15">
         <v>3768.67</v>
@@ -9133,7 +9142,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B110" s="18">
         <v>43.51</v>
@@ -9155,7 +9164,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B111" s="15">
         <v>107.18</v>
@@ -9177,7 +9186,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B112" s="18">
         <v>6.31</v>
@@ -9199,7 +9208,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B113" s="19"/>
       <c r="C113" s="19"/>
@@ -9219,7 +9228,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B114" s="18">
         <v>61.96</v>
@@ -9257,7 +9266,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B115" s="18">
         <v>3.28</v>
@@ -9295,7 +9304,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B116" s="18">
         <v>58.68</v>
@@ -9333,7 +9342,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B117" s="18">
         <v>1.0</v>
@@ -9371,7 +9380,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B118" s="19"/>
       <c r="C118" s="19"/>
@@ -9393,7 +9402,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B119" s="19"/>
       <c r="C119" s="19"/>
@@ -9415,7 +9424,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B120" s="19"/>
       <c r="C120" s="19"/>
@@ -9433,7 +9442,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B121" s="19"/>
       <c r="C121" s="19"/>
@@ -9457,7 +9466,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B122" s="15">
         <v>5055.0</v>
@@ -10375,7 +10384,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10618,37 +10627,37 @@
         <v>33</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -10691,7 +10700,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -10745,7 +10754,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B20" s="15">
         <v>231.59</v>
@@ -10773,7 +10782,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B21" s="15">
         <v>121.84</v>
@@ -10801,7 +10810,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B22" s="15">
         <v>786.37</v>
@@ -10839,7 +10848,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B23" s="15">
         <v>1225.82</v>
@@ -10915,7 +10924,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B25" s="15">
         <v>475.96</v>
@@ -10953,7 +10962,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B26" s="18">
         <v>31.54</v>
@@ -10991,7 +11000,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
@@ -11011,7 +11020,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B28" s="21">
         <v>-120.48</v>
@@ -11049,7 +11058,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B29" s="21">
         <v>-115.07</v>
@@ -11081,7 +11090,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B30" s="20">
         <v>-18.75</v>
@@ -11113,7 +11122,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B31" s="18">
         <v>37.81</v>
@@ -11145,7 +11154,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B32" s="20">
         <v>-24.46</v>
@@ -11177,7 +11186,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B33" s="21">
         <v>-150.47</v>
@@ -11211,7 +11220,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B34" s="18">
         <v>3.21</v>
@@ -11249,7 +11258,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B35" s="21">
         <v>-171.71</v>
@@ -11287,7 +11296,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B36" s="19"/>
       <c r="C36" s="19"/>
@@ -11305,7 +11314,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B37" s="21">
         <v>-187.38</v>
@@ -11343,7 +11352,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B38" s="20">
         <v>-0.01</v>
@@ -11363,7 +11372,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="16" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B39" s="17">
         <v>598.98</v>
@@ -11401,7 +11410,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B40" s="21">
         <v>-113.41</v>
@@ -11439,7 +11448,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B41" s="21">
         <v>-289.53</v>
@@ -11477,7 +11486,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B42" s="20">
         <v>-4.06</v>
@@ -11515,7 +11524,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B43" s="19">
         <v>0.0</v>
@@ -11535,7 +11544,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B44" s="18">
         <v>1.17</v>
@@ -11573,7 +11582,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B45" s="19"/>
       <c r="C45" s="19">
@@ -11609,7 +11618,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B46" s="19"/>
       <c r="C46" s="19">
@@ -11629,7 +11638,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B47" s="19"/>
       <c r="C47" s="19"/>
@@ -11653,7 +11662,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B48" s="19"/>
       <c r="C48" s="19"/>
@@ -11681,7 +11690,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="16" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B49" s="23">
         <v>-405.83</v>
@@ -11719,7 +11728,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B50" s="19">
         <v>0.0</v>
@@ -11753,7 +11762,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B51" s="19">
         <v>0.0</v>
@@ -11821,7 +11830,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B53" s="19">
         <v>0.0</v>
@@ -11859,7 +11868,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B54" s="19">
         <v>0.0</v>
@@ -11921,7 +11930,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B56" s="20">
         <v>-0.42</v>
@@ -11951,7 +11960,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B57" s="20">
         <v>-4.34</v>
@@ -11973,7 +11982,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
@@ -11991,7 +12000,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
@@ -12015,7 +12024,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
@@ -12035,7 +12044,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B61" s="19"/>
       <c r="C61" s="19"/>
@@ -12059,7 +12068,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="16" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B62" s="23">
         <v>-474.62</v>
@@ -12097,7 +12106,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B63" s="21">
         <v>-281.46</v>
@@ -12135,7 +12144,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B64" s="15">
         <v>445.08</v>
@@ -12173,7 +12182,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B65" s="20">
         <v>-1.51</v>
@@ -12211,7 +12220,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B66" s="15">
         <v>159.42</v>
@@ -12249,7 +12258,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="16" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B67" s="23">
         <v>-282.98</v>
@@ -13240,7 +13249,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -13556,7 +13565,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -13609,830 +13618,830 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
+      <c r="A20" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="28" t="s">
-        <v>296</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="B21" s="30">
         <v>11021.4</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <v>9978.66</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>16704.05</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <v>8467.96</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>11438.36</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="31">
         <v>7960.19</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="31">
         <v>3389.48</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="31">
         <v>2383.08</v>
       </c>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="28" t="s">
-        <v>297</v>
-      </c>
-      <c r="B22" s="29">
+      <c r="A22" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="B22" s="30">
         <v>12344.62</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <v>11888.14</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <v>10173.71</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <v>6909.16</v>
       </c>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="29"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="26" t="s">
-        <v>298</v>
-      </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
+      <c r="A23" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="28" t="s">
-        <v>298</v>
-      </c>
-      <c r="B24" s="30">
+      <c r="A24" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="B24" s="31">
         <v>7767.49</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <v>7166.91</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <v>14306.77</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <v>6603.01</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <v>10484.36</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="31">
         <v>7420.08</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="31">
         <v>3412.84</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="31">
         <v>2451.58</v>
       </c>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="28" t="s">
-        <v>299</v>
-      </c>
-      <c r="B25" s="30">
+      <c r="A25" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="B25" s="31">
         <v>9977.37</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <v>10057.18</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="31">
         <v>8973.15</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="31">
         <v>6247.73</v>
       </c>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
+      <c r="A26" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="B27" s="30">
+      <c r="A27" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="B27" s="31">
         <v>125.37</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>113.62</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>258.4</v>
       </c>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="26" t="s">
-        <v>302</v>
-      </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
+      <c r="A28" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
-        <v>303</v>
-      </c>
-      <c r="B29" s="31">
+      <c r="A29" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="B29" s="32">
         <v>3.94</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="32">
         <v>2.01</v>
       </c>
-      <c r="D29" s="31">
+      <c r="D29" s="32">
         <v>4.29</v>
       </c>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="27"/>
+      <c r="A30" s="27" t="s">
+        <v>306</v>
+      </c>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="28" t="s">
-        <v>305</v>
-      </c>
-      <c r="B31" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="C31" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="D31" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31"/>
+      <c r="A31" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="B31" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="C31" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="D31" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="32"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>306</v>
-      </c>
-      <c r="B32" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="C32" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="D32" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
+      <c r="A32" s="29" t="s">
+        <v>308</v>
+      </c>
+      <c r="B32" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="C32" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="D32" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="27"/>
-      <c r="K33" s="27"/>
-      <c r="L33" s="27"/>
+      <c r="A33" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="28" t="s">
-        <v>308</v>
-      </c>
-      <c r="B34" s="32">
+      <c r="A34" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="B34" s="33">
         <v>0.99</v>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="33">
         <v>0.87</v>
       </c>
-      <c r="D34" s="32">
+      <c r="D34" s="33">
         <v>2.86</v>
       </c>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="29"/>
-      <c r="L34" s="29"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
+      <c r="A35" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="B36" s="32">
+      <c r="A36" s="29" t="s">
+        <v>312</v>
+      </c>
+      <c r="B36" s="33">
         <v>1.97</v>
       </c>
-      <c r="C36" s="32">
+      <c r="C36" s="33">
         <v>1.61</v>
       </c>
-      <c r="D36" s="32">
+      <c r="D36" s="33">
         <v>4.02</v>
       </c>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="29"/>
-      <c r="K36" s="29"/>
-      <c r="L36" s="29"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
+      <c r="A37" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="28" t="s">
-        <v>312</v>
-      </c>
-      <c r="B38" s="32">
+      <c r="A38" s="29" t="s">
+        <v>314</v>
+      </c>
+      <c r="B38" s="33">
         <v>25.37</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="33">
         <v>49.7</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="33">
         <v>23.31</v>
       </c>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="29"/>
-      <c r="L38" s="29"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="26" t="s">
-        <v>313</v>
-      </c>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="27"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="27"/>
+      <c r="A39" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
-        <v>314</v>
-      </c>
-      <c r="B40" s="32">
+      <c r="A40" s="29" t="s">
+        <v>316</v>
+      </c>
+      <c r="B40" s="33">
         <v>10.43</v>
       </c>
-      <c r="C40" s="32">
+      <c r="C40" s="33">
         <v>7.97</v>
       </c>
-      <c r="D40" s="32">
+      <c r="D40" s="33">
         <v>19.31</v>
       </c>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="26" t="s">
-        <v>315</v>
-      </c>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="27"/>
+      <c r="A41" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="28"/>
+      <c r="J41" s="28"/>
+      <c r="K41" s="28"/>
+      <c r="L41" s="28"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="28" t="s">
-        <v>316</v>
-      </c>
-      <c r="B42" s="32">
+      <c r="A42" s="29" t="s">
+        <v>318</v>
+      </c>
+      <c r="B42" s="33">
         <v>28.07</v>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="33">
         <v>17.57</v>
       </c>
-      <c r="D42" s="32">
+      <c r="D42" s="33">
         <v>33.0</v>
       </c>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="29"/>
-      <c r="J42" s="29"/>
-      <c r="K42" s="29"/>
-      <c r="L42" s="29"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
+      <c r="A43" s="27" t="s">
+        <v>319</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="28" t="s">
-        <v>318</v>
-      </c>
-      <c r="B44" s="32">
+      <c r="A44" s="29" t="s">
+        <v>320</v>
+      </c>
+      <c r="B44" s="33">
         <v>19.47</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="33">
         <v>13.31</v>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="33">
         <v>26.34</v>
       </c>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="29"/>
-      <c r="J44" s="29"/>
-      <c r="K44" s="29"/>
-      <c r="L44" s="29"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="27"/>
-      <c r="J45" s="27"/>
-      <c r="K45" s="27"/>
-      <c r="L45" s="27"/>
+      <c r="A45" s="27" t="s">
+        <v>321</v>
+      </c>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
-        <v>320</v>
-      </c>
-      <c r="B46" s="33">
+      <c r="A46" s="29" t="s">
+        <v>322</v>
+      </c>
+      <c r="B46" s="34">
         <v>-0.9</v>
       </c>
-      <c r="C46" s="33">
+      <c r="C46" s="34">
         <v>-0.82</v>
       </c>
-      <c r="D46" s="33">
+      <c r="D46" s="34">
         <v>-1.87</v>
       </c>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="27"/>
-      <c r="K47" s="27"/>
-      <c r="L47" s="27"/>
+      <c r="A47" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="28"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="28"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="28" t="s">
-        <v>322</v>
-      </c>
-      <c r="B48" s="32">
+      <c r="A48" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="B48" s="33">
         <v>2.77</v>
       </c>
-      <c r="C48" s="32">
+      <c r="C48" s="33">
         <v>2.28</v>
       </c>
-      <c r="D48" s="32">
+      <c r="D48" s="33">
         <v>4.57</v>
       </c>
-      <c r="E48" s="32">
+      <c r="E48" s="33">
         <v>3.0</v>
       </c>
-      <c r="F48" s="32">
+      <c r="F48" s="33">
         <v>6.45</v>
       </c>
-      <c r="G48" s="32">
+      <c r="G48" s="33">
         <v>8.33</v>
       </c>
-      <c r="H48" s="32">
+      <c r="H48" s="33">
         <v>5.11</v>
       </c>
-      <c r="I48" s="32">
+      <c r="I48" s="33">
         <v>5.94</v>
       </c>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="28" t="s">
-        <v>323</v>
-      </c>
-      <c r="B49" s="32">
+      <c r="A49" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="B49" s="33">
         <v>3.53</v>
       </c>
-      <c r="C49" s="32">
+      <c r="C49" s="33">
         <v>4.09</v>
       </c>
-      <c r="D49" s="32">
+      <c r="D49" s="33">
         <v>4.88</v>
       </c>
-      <c r="E49" s="32">
+      <c r="E49" s="33">
         <v>5.1</v>
       </c>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="26" t="s">
-        <v>324</v>
-      </c>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="27"/>
-      <c r="H50" s="27"/>
-      <c r="I50" s="27"/>
-      <c r="J50" s="27"/>
-      <c r="K50" s="27"/>
-      <c r="L50" s="27"/>
+      <c r="A50" s="27" t="s">
+        <v>326</v>
+      </c>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="28"/>
+      <c r="K50" s="28"/>
+      <c r="L50" s="28"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="28" t="s">
-        <v>325</v>
-      </c>
-      <c r="B51" s="32">
+      <c r="A51" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="B51" s="33">
         <v>9.21</v>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="33">
         <v>7.49</v>
       </c>
-      <c r="D51" s="32">
+      <c r="D51" s="33">
         <v>13.44</v>
       </c>
-      <c r="E51" s="32">
+      <c r="E51" s="33">
         <v>9.49</v>
       </c>
-      <c r="F51" s="32">
+      <c r="F51" s="33">
         <v>21.12</v>
       </c>
-      <c r="G51" s="32">
+      <c r="G51" s="33">
         <v>19.93</v>
       </c>
-      <c r="H51" s="32">
+      <c r="H51" s="33">
         <v>12.27</v>
       </c>
-      <c r="I51" s="32">
+      <c r="I51" s="33">
         <v>14.81</v>
       </c>
-      <c r="J51" s="29"/>
-      <c r="K51" s="29"/>
-      <c r="L51" s="29"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="28" t="s">
-        <v>326</v>
-      </c>
-      <c r="B52" s="32">
+      <c r="A52" s="29" t="s">
+        <v>328</v>
+      </c>
+      <c r="B52" s="33">
         <v>11.24</v>
       </c>
-      <c r="C52" s="32">
+      <c r="C52" s="33">
         <v>12.58</v>
       </c>
-      <c r="D52" s="32">
+      <c r="D52" s="33">
         <v>14.37</v>
       </c>
-      <c r="E52" s="32">
+      <c r="E52" s="33">
         <v>14.87</v>
       </c>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="B53" s="27"/>
-      <c r="C53" s="27"/>
-      <c r="D53" s="27"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="27"/>
-      <c r="H53" s="27"/>
-      <c r="I53" s="27"/>
-      <c r="J53" s="27"/>
-      <c r="K53" s="27"/>
-      <c r="L53" s="27"/>
+      <c r="A53" s="27" t="s">
+        <v>329</v>
+      </c>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="28"/>
+      <c r="J53" s="28"/>
+      <c r="K53" s="28"/>
+      <c r="L53" s="28"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="28" t="s">
-        <v>328</v>
-      </c>
-      <c r="B54" s="32">
+      <c r="A54" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="B54" s="33">
         <v>18.23</v>
       </c>
-      <c r="C54" s="32">
+      <c r="C54" s="33">
         <v>17.13</v>
       </c>
-      <c r="D54" s="32">
+      <c r="D54" s="33">
         <v>16.78</v>
       </c>
-      <c r="E54" s="32">
+      <c r="E54" s="33">
         <v>16.76</v>
       </c>
-      <c r="F54" s="32">
+      <c r="F54" s="33">
         <v>36.2</v>
       </c>
-      <c r="G54" s="32">
+      <c r="G54" s="33">
         <v>28.48</v>
       </c>
-      <c r="H54" s="32">
+      <c r="H54" s="33">
         <v>17.17</v>
       </c>
-      <c r="I54" s="32">
+      <c r="I54" s="33">
         <v>36.99</v>
       </c>
-      <c r="J54" s="29"/>
-      <c r="K54" s="29"/>
-      <c r="L54" s="29"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="28" t="s">
-        <v>329</v>
-      </c>
-      <c r="B55" s="32">
+      <c r="A55" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="B55" s="33">
         <v>19.39</v>
       </c>
-      <c r="C55" s="32">
+      <c r="C55" s="33">
         <v>20.62</v>
       </c>
-      <c r="D55" s="32">
+      <c r="D55" s="33">
         <v>21.1</v>
       </c>
-      <c r="E55" s="32">
+      <c r="E55" s="33">
         <v>24.77</v>
       </c>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="26" t="s">
-        <v>330</v>
-      </c>
-      <c r="B56" s="27"/>
-      <c r="C56" s="27"/>
-      <c r="D56" s="27"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="27"/>
-      <c r="H56" s="27"/>
-      <c r="I56" s="27"/>
-      <c r="J56" s="27"/>
-      <c r="K56" s="27"/>
-      <c r="L56" s="27"/>
+      <c r="A56" s="27" t="s">
+        <v>332</v>
+      </c>
+      <c r="B56" s="28"/>
+      <c r="C56" s="28"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="28"/>
+      <c r="I56" s="28"/>
+      <c r="J56" s="28"/>
+      <c r="K56" s="28"/>
+      <c r="L56" s="28"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="28" t="s">
-        <v>331</v>
-      </c>
-      <c r="B57" s="32">
+      <c r="A57" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="B57" s="33">
         <v>35.75</v>
       </c>
-      <c r="C57" s="32">
+      <c r="C57" s="33">
         <v>70.53</v>
       </c>
-      <c r="D57" s="32">
+      <c r="D57" s="33">
         <v>26.48</v>
       </c>
-      <c r="E57" s="29"/>
-      <c r="F57" s="32">
+      <c r="E57" s="30"/>
+      <c r="F57" s="33">
         <v>59.25</v>
       </c>
-      <c r="G57" s="32">
+      <c r="G57" s="33">
         <v>31.12</v>
       </c>
-      <c r="H57" s="29"/>
-      <c r="I57" s="29"/>
-      <c r="J57" s="29"/>
-      <c r="K57" s="29"/>
-      <c r="L57" s="29"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="28" t="s">
-        <v>332</v>
-      </c>
-      <c r="B58" s="32">
+      <c r="A58" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="B58" s="33">
         <v>81.96</v>
       </c>
-      <c r="C58" s="32">
+      <c r="C58" s="33">
         <v>81.4</v>
       </c>
-      <c r="D58" s="32">
+      <c r="D58" s="33">
         <v>97.66</v>
       </c>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="L58" s="29"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
     </row>
     <row r="59" ht="15.75" customHeight="1"/>
     <row r="60" ht="15.75" customHeight="1"/>
